--- a/Real site.xlsx
+++ b/Real site.xlsx
@@ -10,13 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{9657DA15-40D6-41EA-90AE-BF7BDEA20295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30900" yWindow="1095" windowWidth="28800" windowHeight="19170" xr2:uid="{29EAC97B-935B-458A-AC37-F4651EFD24BD}"/>
+    <workbookView xWindow="-38520" yWindow="60" windowWidth="38640" windowHeight="21120" xr2:uid="{29EAC97B-935B-458A-AC37-F4651EFD24BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
